--- a/tests/workbooktests/workbooks/test_parameter.xlsx
+++ b/tests/workbooktests/workbooks/test_parameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA00667C-B6F3-4F70-BF72-9A48C4E1E2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D873DCF-83BA-4F8C-8C85-B2B4EB7E3489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13530" yWindow="-19245" windowWidth="23175" windowHeight="16410" xr2:uid="{45A6C063-5495-498A-86BB-E2019A1EF4EC}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{45A6C063-5495-498A-86BB-E2019A1EF4EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -465,14 +465,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50F4899A-9CD4-44E7-BDF8-8FF10221624B}">
-  <dimension ref="A2:E38"/>
+  <dimension ref="A2:C38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="49.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -480,7 +480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -492,7 +492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>2</v>
       </c>
@@ -501,7 +501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>3</v>
       </c>
@@ -510,83 +510,74 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" t="str" cm="1">
-        <f t="array" ref="B6">_xll.qlPositiveConstraint()</f>
-        <v>⚡[test_parameter.xlsx]Sheet1!R6C2PositiveConstraint,A</v>
+      <c r="B6" t="e" cm="1">
+        <f t="array" aca="1" ref="B6" ca="1">_xll.qlPositiveConstraint()</f>
+        <v>#VALUE!</v>
       </c>
       <c r="C6">
         <f>$B$2</f>
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B9" t="str" cm="1">
-        <f t="array" ref="B9">_xll.qlConstantParameter(B6)</f>
-        <v>⚡[test_parameter.xlsx]Sheet1!R9C2ConstantParameter,A</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" t="e" cm="1">
+        <f t="array" aca="1" ref="B9" ca="1">_xll.qlConstantParameter(B6)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
-      <c r="B10" t="str" cm="1">
-        <f t="array" ref="B10">_xll.qlConstantParameter(B6,B2)</f>
-        <v>⚡[test_parameter.xlsx]Sheet1!R10C2ConstantParameter,A</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" t="e" cm="1">
+        <f t="array" aca="1" ref="B10" ca="1">_xll.qlConstantParameter(B6,B2)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
-      <c r="B11" t="str" cm="1">
-        <f t="array" ref="B11">_xll.qlPiecewiseConstantParameter(B3:B5,C3:C6,B6)</f>
-        <v>⚡[test_parameter.xlsx]Sheet1!R11C2PiecewiseConstantParameter,A</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" t="e" cm="1">
+        <f t="array" aca="1" ref="B11" ca="1">_xll.qlPiecewiseConstantParameter(B3:B5,C3:C6,B6)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
-      <c r="B13" cm="1">
-        <f t="array" ref="B13">_xll.qlParameterParams(B9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B13" t="e" cm="1">
+        <f t="array" aca="1" ref="B13" ca="1">_xll.qlParameterParams(B9)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>5</v>
       </c>
-      <c r="B14" cm="1">
-        <f t="array" ref="B14">_xll.qlParameterParams(B10)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B14" t="e" cm="1">
+        <f t="array" aca="1" ref="B14" ca="1">_xll.qlParameterParams(B10)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>5</v>
       </c>
-      <c r="B15" cm="1">
-        <f t="array" ref="B15:E15">TRANSPOSE(_xll.qlParameterParams(B11))</f>
-        <v>5</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B15" t="e" cm="1">
+        <f t="array" aca="1" ref="B15" ca="1">TRANSPOSE(_xll.qlParameterParams(B11))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -594,7 +585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -602,148 +593,139 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>7</v>
       </c>
-      <c r="B20" t="b" cm="1">
-        <f t="array" ref="B20">_xll.qlParameterSetParam(B9,$B$17,$B$18)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B20" t="e" cm="1">
+        <f t="array" aca="1" ref="B20" ca="1">_xll.qlParameterSetParam(B9,$B$17,$B$18)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>7</v>
       </c>
-      <c r="B21" t="b" cm="1">
-        <f t="array" ref="B21">_xll.qlParameterSetParam(B10,$B$17,$B$18)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B21" t="e" cm="1">
+        <f t="array" aca="1" ref="B21" ca="1">_xll.qlParameterSetParam(B10,$B$17,$B$18)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>7</v>
       </c>
-      <c r="B22" t="b" cm="1">
-        <f t="array" ref="B22">_xll.qlParameterSetParam(B11,$B$17,$B$18)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B22" t="e" cm="1">
+        <f t="array" aca="1" ref="B22" ca="1">_xll.qlParameterSetParam(B11,$B$17,$B$18)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>5</v>
       </c>
-      <c r="B24" cm="1">
-        <f t="array" ref="B24">_xll.qlParameterParams(B9,B20)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B24" t="e" cm="1">
+        <f t="array" aca="1" ref="B24" ca="1">_xll.qlParameterParams(B9,B20)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
-      <c r="B25" cm="1">
-        <f t="array" ref="B25">_xll.qlParameterParams(B10,B21)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B25" t="e" cm="1">
+        <f t="array" aca="1" ref="B25" ca="1">_xll.qlParameterParams(B10,B21)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>5</v>
       </c>
-      <c r="B26" cm="1">
-        <f t="array" ref="B26:E26">TRANSPOSE(_xll.qlParameterParams(B11,B22))</f>
-        <v>5</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>2</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B26" t="e" cm="1">
+        <f t="array" aca="1" ref="B26" ca="1">TRANSPOSE(_xll.qlParameterParams(B11,B22))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>8</v>
       </c>
-      <c r="B28" t="b" cm="1">
-        <f t="array" ref="B28">_xll.qlParameterTestParams($B$9,B18)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B28" t="e" cm="1">
+        <f t="array" aca="1" ref="B28" ca="1">_xll.qlParameterTestParams($B$9,B18)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>8</v>
       </c>
-      <c r="B29" t="b" cm="1">
-        <f t="array" ref="B29">_xll.qlParameterTestParams($B$9,B18)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B29" t="e" cm="1">
+        <f t="array" aca="1" ref="B29" ca="1">_xll.qlParameterTestParams($B$9,B18)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>8</v>
       </c>
-      <c r="B30" t="b" cm="1">
-        <f t="array" ref="B30">_xll.qlParameterTestParams($B$9,B18)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B30" t="e" cm="1">
+        <f t="array" aca="1" ref="B30" ca="1">_xll.qlParameterTestParams($B$9,B18)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>9</v>
       </c>
-      <c r="B32" cm="1">
-        <f t="array" ref="B32">_xll.qlParameterSize(B9)</f>
-        <v>1</v>
+      <c r="B32" t="e" cm="1">
+        <f t="array" aca="1" ref="B32" ca="1">_xll.qlParameterSize(B9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>9</v>
       </c>
-      <c r="B33" cm="1">
-        <f t="array" ref="B33">_xll.qlParameterSize(B10)</f>
-        <v>1</v>
+      <c r="B33" t="e" cm="1">
+        <f t="array" aca="1" ref="B33" ca="1">_xll.qlParameterSize(B10)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>9</v>
       </c>
-      <c r="B34" cm="1">
-        <f t="array" ref="B34">_xll.qlParameterSize(B11)</f>
-        <v>4</v>
+      <c r="B34" t="e" cm="1">
+        <f t="array" aca="1" ref="B34" ca="1">_xll.qlParameterSize(B11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>10</v>
       </c>
-      <c r="B36" t="str" cm="1">
-        <f t="array" ref="B36">_xll.qlParameterConstraint(B9)</f>
-        <v>⚡[test_parameter.xlsx]Sheet1!R36C2Constraint,A</v>
+      <c r="B36" t="e" cm="1">
+        <f t="array" aca="1" ref="B36" ca="1">_xll.qlParameterConstraint(B9)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>10</v>
       </c>
-      <c r="B37" t="str" cm="1">
-        <f t="array" ref="B37">_xll.qlParameterConstraint(B10)</f>
-        <v>⚡[test_parameter.xlsx]Sheet1!R37C2Constraint,A</v>
+      <c r="B37" t="e" cm="1">
+        <f t="array" aca="1" ref="B37" ca="1">_xll.qlParameterConstraint(B10)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>10</v>
       </c>
-      <c r="B38" t="str" cm="1">
-        <f t="array" ref="B38">_xll.qlParameterConstraint(B11)</f>
-        <v>⚡[test_parameter.xlsx]Sheet1!R38C2Constraint,A</v>
+      <c r="B38" t="e" cm="1">
+        <f t="array" aca="1" ref="B38" ca="1">_xll.qlParameterConstraint(B11)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
